--- a/scr/uploads/Students.xlsx
+++ b/scr/uploads/Students.xlsx
@@ -467,7 +467,7 @@
         <v>08011111111</v>
       </c>
       <c r="K2" s="1">
-        <v>46245.872525844905</v>
+        <v>46282.709844363424</v>
       </c>
     </row>
   </sheetData>
